--- a/app技术文档.xlsx
+++ b/app技术文档.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11805"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1812,11 +1812,19 @@
           </a:r>
           <a:r>
             <a:rPr lang="en-US" altLang="zh-CN" sz="1400">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
               <a:sym typeface="+mn-ea"/>
             </a:rPr>
             <a:t>hppt://127.0.0.1:8081</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1400"/>
+          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1400">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+            <a:sym typeface="+mn-ea"/>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -1924,26 +1932,50 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1400"/>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
             <a:t>./gradlew assembleRelease(</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="zh-CN" altLang="en-US" sz="1400"/>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
             <a:t>更新</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1400"/>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
             <a:t>3.16:</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="zh-CN" altLang="en-US" sz="1400"/>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1400">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
             <a:t>当前使用</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" altLang="zh-CN" sz="1400"/>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1400">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
             <a:t>)</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1400"/>
+          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1400">
+            <a:solidFill>
+              <a:srgbClr val="FF0000"/>
+            </a:solidFill>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
